--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2355,10 +2355,10 @@
         <v>471451</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>22000</v>
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-04-30</t>
+          <t>Steam 인기 차트 — 2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3699,28 +3699,28 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="2" t="n">
         <v>14439</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="2" t="n">
         <v>94.3</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="2" t="n">
         <v>499828</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>50</v>
+      <c r="F50" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-04-30</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-04-30</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-01</t>
+          <t>Steam 인기 차트 — 2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-01</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-02</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-01</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-02</t>
+          <t>Steam 인기 차트 — 2026-05-03</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-02</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-03</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-02</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,10 +2004,10 @@
         <v>713071</v>
       </c>
       <c r="I39" t="n">
-        <v>23100</v>
+        <v>66000</v>
       </c>
       <c r="J39" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>66000</v>
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,10 +2160,10 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>6960</v>
+        <v>34800</v>
       </c>
       <c r="J43" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>34800</v>
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-03</t>
+          <t>Steam 인기 차트 — 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3474,28 +3474,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" t="n">
         <v>22265</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>844921</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>23100</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>65</v>
+      <c r="F41" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3574,28 +3574,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" t="n">
         <v>15893</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" t="n">
         <v>835349</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>6960</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>80</v>
+      <c r="F45" t="n">
+        <v>34800</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-03</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-03</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>66000</v>
+        <v>49500</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,19 +2277,19 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9460</v>
+        <v>21000</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>43000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-04</t>
+          <t>Steam 인기 차트 — 2026-05-05</t>
         </is>
       </c>
     </row>
@@ -3049,28 +3049,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="4" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
+      <c r="F24" s="4" t="n">
+        <v>49500</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="2" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="2" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>9460</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>78</v>
+      <c r="F48" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-04</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-05</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-04</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-05</t>
+          <t>Steam 인기 차트 — 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
+      <c r="F51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-05</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-05</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2043,10 +2043,10 @@
         <v>630223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8600</v>
+        <v>21500</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21500</v>
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-07</t>
+          <t>Steam 인기 차트 — 2026-05-08</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>50</v>
+      <c r="F26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3499,28 +3499,28 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="2" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="2" t="n">
         <v>797216</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>8600</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>60</v>
+      <c r="F42" s="2" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-07</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-07</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-08</t>
+          <t>Steam 인기 차트 — 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-08</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-08</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-09</t>
+          <t>Steam 인기 차트 — 2026-05-10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-09</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-10</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-09</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-10</t>
+          <t>Steam 인기 차트 — 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-10</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-10</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>49500</v>
+        <v>66000</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="J27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-11</t>
+          <t>Steam 인기 차트 — 2026-05-12</t>
         </is>
       </c>
     </row>
@@ -3049,28 +3049,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="2" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>49500</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>25</v>
+      <c r="F24" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>50</v>
+      <c r="F29" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-11</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-12</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-11</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-12</t>
+          <t>Steam 인기 차트 — 2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-12</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-12</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10700</v>
+        <v>5350</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-13</t>
+          <t>Steam 인기 차트 — 2026-05-14</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
+      <c r="F36" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-13</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-14</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-13</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1653,10 +1653,10 @@
         <v>872384</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>16000</v>
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>24800</v>
+        <v>6200</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-14</t>
+          <t>Steam 인기 차트 — 2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3249,28 +3249,28 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="4" t="n">
         <v>50662</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="4" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>886195</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
+      <c r="F32" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -3674,28 +3674,28 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="4" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" t="n">
-        <v>24800</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
+      <c r="F49" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-14</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-14</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-15</t>
+          <t>Steam 인기 차트 — 2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-15</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-16</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-15</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-16</t>
+          <t>Steam 인기 차트 — 2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-16</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-17</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-16</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-17</t>
+          <t>Steam 인기 차트 — 2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-17</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-17</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-18</t>
+          <t>Steam 인기 차트 — 2026-05-19</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-18</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-19</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-18</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>16500</v>
+        <v>10890</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-19</t>
+          <t>Steam 인기 차트 — 2026-05-20</t>
         </is>
       </c>
     </row>
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="4" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
+      <c r="F31" s="4" t="n">
+        <v>10890</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>30</v>
+      <c r="F51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-19</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-20</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-19</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-20</t>
+          <t>Steam 인기 차트 — 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-20</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-20</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1653,10 +1653,10 @@
         <v>872384</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>16000</v>
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-21</t>
+          <t>Steam 인기 차트 — 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -3249,28 +3249,28 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="2" t="n">
         <v>50662</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="2" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>886195</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>50</v>
+      <c r="F32" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-21</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-21</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-22</t>
+          <t>Steam 인기 차트 — 2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-22</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-23</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-22</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-23</t>
+          <t>Steam 인기 차트 — 2026-05-24</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-23</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-24</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-23</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>6200</v>
+        <v>24800</v>
       </c>
       <c r="J47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-24</t>
+          <t>Steam 인기 차트 — 2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3674,28 +3674,28 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>75</v>
+      <c r="F49" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-24</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-24</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-25</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-25</t>
+          <t>Steam 인기 차트 — 2026-05-26</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-25</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-26</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-25</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>32000</v>
+        <v>24000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-26</t>
+          <t>Steam 인기 차트 — 2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="F7" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-26</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-27</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-26</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5350</v>
+        <v>10700</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>79800</v>
+        <v>11970</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-27</t>
+          <t>Steam 인기 차트 — 2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>50</v>
+      <c r="F36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" t="n">
-        <v>79800</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+      <c r="F43" s="4" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="44">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-27</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-28</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-27</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-28</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-28</t>
+          <t>Steam 인기 차트 — 2026-05-29</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-28</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-28</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-29</t>
+          <t>Steam 인기 차트 — 2026-05-30</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-29</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-29</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-30</t>
+          <t>Steam 인기 차트 — 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="4" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
+      <c r="F46" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-30</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-30</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-31</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-05-31</t>
+          <t>Steam 인기 차트 — 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-05-31</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-05-31</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-01</t>
+          <t>Steam 인기 차트 — 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-01</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-02</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-01</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>10890</v>
+        <v>16500</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-02</t>
+          <t>Steam 인기 차트 — 2026-06-03</t>
         </is>
       </c>
     </row>
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>34</v>
+      <c r="F31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-02</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-03</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-02</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-03</t>
+          <t>Steam 인기 차트 — 2026-06-04</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-03</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-04</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-03</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>84800</v>
+        <v>35620</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K15" t="n">
         <v>84800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>20500</v>
+        <v>4510</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-04</t>
+          <t>Steam 인기 차트 — 2026-06-05</t>
         </is>
       </c>
     </row>
@@ -2874,28 +2874,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" t="n">
-        <v>84800</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
+      <c r="F17" s="4" t="n">
+        <v>35620</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -3274,28 +3274,28 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="4" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
+      <c r="F33" s="4" t="n">
+        <v>4510</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-04</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-05</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-04</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-05</t>
+          <t>Steam 인기 차트 — 2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-05</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-06</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-05</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-06</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -834,19 +834,19 @@
         <v>1111720</v>
       </c>
       <c r="I9" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>64800</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,19 +2082,19 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>11970</v>
+        <v/>
       </c>
       <c r="J41" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>79800</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,19 +2394,19 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>21500</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-06</t>
+          <t>Steam 인기 차트 — 2026-06-07</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>1150098</v>
       </c>
       <c r="F11" t="n">
-        <v>64800</v>
+        <v/>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>11970</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>85</v>
+      <c r="F43" t="n">
+        <v/>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3742,7 +3742,7 @@
         <v>768779</v>
       </c>
       <c r="F51" t="n">
-        <v>21500</v>
+        <v/>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-06</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-07</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-06</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -834,19 +834,19 @@
         <v>1111720</v>
       </c>
       <c r="I9" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v/>
+        <v>64800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,19 +2082,19 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v/>
+        <v>11970</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K41" t="n">
-        <v/>
+        <v>79800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,19 +2394,19 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v/>
+        <v>21500</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-07</t>
+          <t>Steam 인기 차트 — 2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>1150098</v>
       </c>
       <c r="F11" t="n">
-        <v/>
+        <v>64800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+      <c r="F43" s="4" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="44">
@@ -3742,7 +3742,7 @@
         <v>768779</v>
       </c>
       <c r="F51" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-07</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-07</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10500</v>
+        <v>5250</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>11970</v>
+        <v>79800</v>
       </c>
       <c r="J41" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-08</t>
+          <t>Steam 인기 차트 — 2026-06-09</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="4" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
+      <c r="F26" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>11970</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>85</v>
+      <c r="F43" t="n">
+        <v>79800</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-08</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-09</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-08</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>24000</v>
+        <v>32000</v>
       </c>
       <c r="J5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-09</t>
+          <t>Steam 인기 차트 — 2026-06-10</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>25</v>
+      <c r="F7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-09</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-10</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-09</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-10</t>
+          <t>Steam 인기 차트 — 2026-06-11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-10</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-11</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-10</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>4510</v>
+        <v>20500</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,10 +2277,10 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21000</v>
+        <v>5250</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>21000</v>
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-11</t>
+          <t>Steam 인기 차트 — 2026-06-12</t>
         </is>
       </c>
     </row>
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
+      <c r="F29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -3274,28 +3274,28 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>4510</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>78</v>
+      <c r="F33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="4" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
+      <c r="F48" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-11</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-12</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-11</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-12</t>
+          <t>Steam 인기 차트 — 2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-12</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-13</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-12</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-13</t>
+          <t>Steam 인기 차트 — 2026-06-14</t>
         </is>
       </c>
     </row>
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>40</v>
+      <c r="F46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-13</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-14</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-13</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-14</t>
+          <t>Steam 인기 차트 — 2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-14</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-14</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-15</t>
+          <t>Steam 인기 차트 — 2026-06-16</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-15</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-16</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-15</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2043,10 +2043,10 @@
         <v>630223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21500</v>
+        <v>8600</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21500</v>
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-16</t>
+          <t>Steam 인기 차트 — 2026-06-17</t>
         </is>
       </c>
     </row>
@@ -3499,28 +3499,28 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="4" t="n">
         <v>44886</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>797216</v>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
+      <c r="F42" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-16</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-17</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-16</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1926,10 +1926,10 @@
         <v>88027</v>
       </c>
       <c r="I37" t="n">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
         <v>37500</v>
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-17</t>
+          <t>Steam 인기 차트 — 2026-06-18</t>
         </is>
       </c>
     </row>
@@ -3424,28 +3424,28 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="4" t="n">
         <v>5831</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>110623</v>
       </c>
-      <c r="F39" t="n">
-        <v>37500</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
+      <c r="F39" s="4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-17</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-18</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-17</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>35620</v>
+        <v>84800</v>
       </c>
       <c r="J15" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>84800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,10 +2004,10 @@
         <v>713071</v>
       </c>
       <c r="I39" t="n">
-        <v>66000</v>
+        <v>19800</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K39" t="n">
         <v>66000</v>
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,10 +2160,10 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>34800</v>
+        <v>3480</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K43" t="n">
         <v>34800</v>
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-18</t>
+          <t>Steam 인기 차트 — 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -2874,28 +2874,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>35620</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>58</v>
+      <c r="F17" t="n">
+        <v>84800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3474,28 +3474,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="4" t="n">
         <v>22265</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>844921</v>
       </c>
-      <c r="F41" t="n">
-        <v>66000</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
+      <c r="F41" s="4" t="n">
+        <v>19800</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="42">
@@ -3574,28 +3574,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="4" t="n">
         <v>15893</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>835349</v>
       </c>
-      <c r="F45" t="n">
-        <v>34800</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
+      <c r="F45" s="4" t="n">
+        <v>3480</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="46">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-18</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-18</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-19</t>
+          <t>Steam 인기 차트 — 2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-19</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-20</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-19</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-20</t>
+          <t>Steam 인기 차트 — 2026-06-21</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-20</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-21</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-20</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-21</t>
+          <t>Steam 인기 차트 — 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-21</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-21</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-22</t>
+          <t>Steam 인기 차트 — 2026-06-23</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>50</v>
+      <c r="F26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-22</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-23</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-22</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-23</t>
+          <t>Steam 인기 차트 — 2026-06-24</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-23</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-24</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-23</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-24</t>
+          <t>Steam 인기 차트 — 2026-06-25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-24</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-25</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-24</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-25</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>32000</v>
+        <v>22400</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -912,10 +912,10 @@
         <v>940221</v>
       </c>
       <c r="I11" t="n">
-        <v>11000</v>
+        <v>2200</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K11" t="n">
         <v>11000</v>
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>84800</v>
+        <v>35620</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K15" t="n">
         <v>84800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1107,10 +1107,10 @@
         <v>775883</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44800</v>
+        <v>33600</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>44800</v>
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1224,10 +1224,10 @@
         <v>1373979</v>
       </c>
       <c r="I19" t="n">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
         <v>11000</v>
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1302,10 +1302,10 @@
         <v>876898</v>
       </c>
       <c r="I21" t="n">
-        <v>5600</v>
+        <v>4480</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
         <v>5600</v>
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>66000</v>
+        <v>49500</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10500</v>
+        <v>5250</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1653,10 +1653,10 @@
         <v>872384</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16000</v>
+        <v>9600</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>16000</v>
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>20500</v>
+        <v>4510</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10700</v>
+        <v>3210</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>79800</v>
+        <v>11970</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>24800</v>
+        <v>6200</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2355,10 +2355,10 @@
         <v>471451</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>22000</v>
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-25</t>
+          <t>Steam 인기 차트 — 2026-06-26</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="F7" s="4" t="n">
+        <v>22400</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -2774,28 +2774,28 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="4" t="n">
         <v>25122</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>963983</v>
       </c>
-      <c r="F13" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
+      <c r="F13" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -2874,53 +2874,53 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" t="n">
-        <v>84800</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
+      <c r="F17" s="4" t="n">
+        <v>35620</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>HELLDIVERS 2</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="4" t="n">
         <v>53399</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>1017635</v>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>44800</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
+      <c r="F18" s="4" t="n">
+        <v>33600</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2974,28 +2974,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="4" t="n">
         <v>24580</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>1409473</v>
       </c>
-      <c r="F21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
+      <c r="F21" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -3024,53 +3024,53 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="4" t="n">
         <v>91184</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
         <v>894458</v>
       </c>
-      <c r="F23" t="n">
-        <v>5600</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
+      <c r="F23" s="4" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="4" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
+      <c r="F24" s="4" t="n">
+        <v>49500</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="4" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
+      <c r="F26" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -3249,53 +3249,53 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="4" t="n">
         <v>50662</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="4" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>886195</v>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
+      <c r="F32" s="4" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="4" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
+      <c r="F33" s="4" t="n">
+        <v>4510</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
+      <c r="F36" s="4" t="n">
+        <v>3210</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="37">
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" t="n">
-        <v>79800</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+      <c r="F43" s="4" t="n">
+        <v>11970</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="44">
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="4" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
+      <c r="F46" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -3674,78 +3674,78 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="4" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" t="n">
-        <v>24800</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
+      <c r="F49" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="4" t="n">
         <v>14439</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="4" t="n">
         <v>94.3</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="4" t="n">
         <v>499828</v>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
+      <c r="F50" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
+      <c r="F51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-25</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-26</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-25</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>16500</v>
+        <v>10890</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-26</t>
+          <t>Steam 인기 차트 — 2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="4" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
+      <c r="F31" s="4" t="n">
+        <v>10890</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-26</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-27</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-26</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-27</t>
+          <t>Steam 인기 차트 — 2026-06-28</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-27</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-28</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-27</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-28</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-28</t>
+          <t>Steam 인기 차트 — 2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-28</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-28</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-29</t>
+          <t>Steam 인기 차트 — 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-29</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-29</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-06-30</t>
+          <t>Steam 인기 차트 — 2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-06-30</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-06-30</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-01</t>
+          <t>Steam 인기 차트 — 2026-07-02</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-01</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-02</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-01</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-02</t>
+          <t>Steam 인기 차트 — 2026-07-03</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-02</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-03</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-02</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-03</t>
+          <t>Steam 인기 차트 — 2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-03</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-04</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-03</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-04</t>
+          <t>Steam 인기 차트 — 2026-07-05</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-04</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-05</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-04</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-05</t>
+          <t>Steam 인기 차트 — 2026-07-06</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-05</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-06</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-05</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-06</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-06</t>
+          <t>Steam 인기 차트 — 2026-07-07</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-06</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-07</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-06</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-07</t>
+          <t>Steam 인기 차트 — 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-07</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-07</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-08</t>
+          <t>Steam 인기 차트 — 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-08</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-08</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -912,10 +912,10 @@
         <v>940221</v>
       </c>
       <c r="I11" t="n">
-        <v>2200</v>
+        <v>11000</v>
       </c>
       <c r="J11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>11000</v>
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>35620</v>
+        <v>84800</v>
       </c>
       <c r="J15" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>84800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1107,10 +1107,10 @@
         <v>775883</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33600</v>
+        <v>44800</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>44800</v>
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1224,10 +1224,10 @@
         <v>1373979</v>
       </c>
       <c r="I19" t="n">
-        <v>5500</v>
+        <v>11000</v>
       </c>
       <c r="J19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>11000</v>
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1302,10 +1302,10 @@
         <v>876898</v>
       </c>
       <c r="I21" t="n">
-        <v>4480</v>
+        <v>5600</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>5600</v>
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>49500</v>
+        <v>66000</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="J27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1653,10 +1653,10 @@
         <v>872384</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>9600</v>
+        <v>16000</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>16000</v>
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>4510</v>
+        <v>20500</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3210</v>
+        <v>10700</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1926,10 +1926,10 @@
         <v>88027</v>
       </c>
       <c r="I37" t="n">
-        <v>30000</v>
+        <v>37500</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>37500</v>
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,10 +2004,10 @@
         <v>713071</v>
       </c>
       <c r="I39" t="n">
-        <v>19800</v>
+        <v>66000</v>
       </c>
       <c r="J39" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>66000</v>
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2043,10 +2043,10 @@
         <v>630223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8600</v>
+        <v>21500</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21500</v>
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>11970</v>
+        <v>79800</v>
       </c>
       <c r="J41" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,10 +2160,10 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>3480</v>
+        <v>34800</v>
       </c>
       <c r="J43" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>34800</v>
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,10 +2277,10 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5250</v>
+        <v>21000</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>21000</v>
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2355,10 +2355,10 @@
         <v>471451</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>22000</v>
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-09</t>
+          <t>Steam 인기 차트 — 2026-07-10</t>
         </is>
       </c>
     </row>
@@ -2774,28 +2774,28 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Left 4 Dead 2</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" t="n">
         <v>25122</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" t="n">
         <v>97.5</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" t="n">
         <v>963983</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>80</v>
+      <c r="F13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2874,53 +2874,53 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>35620</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>58</v>
+      <c r="F17" t="n">
+        <v>84800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>HELLDIVERS 2</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="2" t="n">
         <v>53399</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="2" t="n">
         <v>76.2</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>1017635</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>33600</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>25</v>
+      <c r="F18" s="2" t="n">
+        <v>44800</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2974,28 +2974,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" t="n">
         <v>24580</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>97.5</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>1409473</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>50</v>
+      <c r="F21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3024,53 +3024,53 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Wallpaper Engine</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" t="n">
         <v>91184</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" t="n">
         <v>98</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" t="n">
         <v>894458</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>4480</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>20</v>
+      <c r="F23" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="2" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>49500</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>25</v>
+      <c r="F24" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>50</v>
+      <c r="F26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>50</v>
+      <c r="F29" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3249,53 +3249,53 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Stardew Valley</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="2" t="n">
         <v>50662</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="2" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>886195</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>40</v>
+      <c r="F32" s="2" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>4510</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>78</v>
+      <c r="F33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>3210</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>70</v>
+      <c r="F36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3424,28 +3424,28 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Last Epoch</t>
         </is>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" t="n">
         <v>5831</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" t="n">
         <v>110623</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>20</v>
+      <c r="F39" t="n">
+        <v>37500</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3474,78 +3474,78 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" t="n">
         <v>22265</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>844921</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>19800</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>70</v>
+      <c r="F41" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="2" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="2" t="n">
         <v>797216</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>8600</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>60</v>
+      <c r="F42" s="2" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>11970</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>85</v>
+      <c r="F43" t="n">
+        <v>79800</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3574,53 +3574,53 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" t="n">
         <v>15893</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" t="n">
         <v>835349</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>3480</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>90</v>
+      <c r="F45" t="n">
+        <v>34800</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>40</v>
+      <c r="F46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="2" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="2" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>75</v>
+      <c r="F48" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3699,53 +3699,53 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="2" t="n">
         <v>14439</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="2" t="n">
         <v>94.3</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="2" t="n">
         <v>499828</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>50</v>
+      <c r="F50" s="2" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>30</v>
+      <c r="F51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-09</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-10</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-09</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-10</t>
+          <t>Steam 인기 차트 — 2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-10</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-11</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-10</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-11</t>
+          <t>Steam 인기 차트 — 2026-07-12</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-11</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-12</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-11</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10700</v>
+        <v>5350</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2355,10 +2355,10 @@
         <v>471451</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>22000</v>
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-12</t>
+          <t>Steam 인기 차트 — 2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
+      <c r="F36" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -3699,28 +3699,28 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="4" t="n">
         <v>14439</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="4" t="n">
         <v>94.3</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="4" t="n">
         <v>499828</v>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
+      <c r="F50" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="51">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-12</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-13</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-12</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-13</t>
+          <t>Steam 인기 차트 — 2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="4" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
+      <c r="F46" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-13</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-14</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-13</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-14</t>
+          <t>Steam 인기 차트 — 2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-14</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-15</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-14</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-15</t>
+          <t>Steam 인기 차트 — 2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-15</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-16</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-15</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-16</t>
+          <t>Steam 인기 차트 — 2026-07-17</t>
         </is>
       </c>
     </row>
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
+      <c r="F51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-16</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-17</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-16</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-17</t>
+          <t>Steam 인기 차트 — 2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-17</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-18</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-17</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-18</t>
+          <t>Steam 인기 차트 — 2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-18</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-18</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-19</t>
+          <t>Steam 인기 차트 — 2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-19</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-20</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-19</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>84800</v>
+        <v>35620</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K15" t="n">
         <v>84800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>6200</v>
+        <v>24800</v>
       </c>
       <c r="J47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-20</t>
+          <t>Steam 인기 차트 — 2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2874,28 +2874,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" t="n">
-        <v>84800</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
+      <c r="F17" s="4" t="n">
+        <v>35620</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -3674,28 +3674,28 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>75</v>
+      <c r="F49" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-20</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-20</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-21</t>
+          <t>Steam 인기 차트 — 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-21</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-21</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10500</v>
+        <v>5250</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-22</t>
+          <t>Steam 인기 차트 — 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="4" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
+      <c r="F26" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-22</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-22</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>22400</v>
+        <v>32000</v>
       </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>10890</v>
+        <v>16500</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-23</t>
+          <t>Steam 인기 차트 — 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>22400</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>30</v>
+      <c r="F7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>34</v>
+      <c r="F31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-23</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-23</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-24</t>
+          <t>Steam 인기 차트 — 2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-24</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-25</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-24</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-25</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-25</t>
+          <t>Steam 인기 차트 — 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-25</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-25</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5350</v>
+        <v>10700</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2355,19 +2355,19 @@
         <v>471451</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11000</v>
+        <v>32000</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-26</t>
+          <t>Steam 인기 차트 — 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="2" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="2" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="2" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>50</v>
+      <c r="F36" s="2" t="n">
+        <v>10700</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3699,28 +3699,28 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Valheim</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="2" t="n">
         <v>14439</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="2" t="n">
         <v>94.3</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="2" t="n">
         <v>499828</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>50</v>
+      <c r="F50" s="2" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-26</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-26</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,10 +2004,10 @@
         <v>713071</v>
       </c>
       <c r="I39" t="n">
-        <v>66000</v>
+        <v>19800</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K39" t="n">
         <v>66000</v>
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,10 +2160,10 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>34800</v>
+        <v>6960</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K43" t="n">
         <v>34800</v>
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,10 +2277,10 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21000</v>
+        <v>5250</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>21000</v>
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-27</t>
+          <t>Steam 인기 차트 — 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3474,28 +3474,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="4" t="n">
         <v>22265</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>844921</v>
       </c>
-      <c r="F41" t="n">
-        <v>66000</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
+      <c r="F41" s="4" t="n">
+        <v>19800</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="42">
@@ -3574,53 +3574,53 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="4" t="n">
         <v>15893</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>835349</v>
       </c>
-      <c r="F45" t="n">
-        <v>34800</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
+      <c r="F45" s="4" t="n">
+        <v>6960</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>40</v>
+      <c r="F46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="4" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
+      <c r="F48" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-27</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-27</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-28</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-28</t>
+          <t>Steam 인기 차트 — 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-28</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-28</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-29</t>
+          <t>Steam 인기 차트 — 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
+      <c r="F29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-29</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-29</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>66000</v>
+        <v>46200</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-30</t>
+          <t>Steam 인기 차트 — 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -3049,28 +3049,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="4" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
+      <c r="F24" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>30</v>
+      <c r="F51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-30</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-30</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-31</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-07-31</t>
+          <t>Steam 인기 차트 — 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-07-31</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-07-31</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-01</t>
+          <t>Steam 인기 차트 — 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-01</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-01</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-02</t>
+          <t>Steam 인기 차트 — 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-02</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-02</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,19 +1068,19 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>35620</v>
+        <v>45800</v>
       </c>
       <c r="J15" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>84800</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-03</t>
+          <t>Steam 인기 차트 — 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -2874,28 +2874,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>35620</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>58</v>
+      <c r="F17" t="n">
+        <v>45800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-03</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-03</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-04</t>
+          <t>Steam 인기 차트 — 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-04</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-04</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5250</v>
+        <v>10500</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-05</t>
+          <t>Steam 인기 차트 — 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="2" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>50</v>
+      <c r="F26" s="2" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-05</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-05</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-06</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1341,10 +1341,10 @@
         <v>736688</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46200</v>
+        <v>66000</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>66000</v>
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-06</t>
+          <t>Steam 인기 차트 — 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3049,28 +3049,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Baldur's Gate 3</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="2" t="n">
         <v>54771</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>96.8</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>760662</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>46200</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>30</v>
+      <c r="F24" s="2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-06</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-06</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-07</t>
+          <t>Steam 인기 차트 — 2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-07</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-07</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-08</t>
+          <t>Steam 인기 차트 — 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-08</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-08</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-09</t>
+          <t>Steam 인기 차트 — 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-09</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-09</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2004,10 +2004,10 @@
         <v>713071</v>
       </c>
       <c r="I39" t="n">
-        <v>19800</v>
+        <v>66000</v>
       </c>
       <c r="J39" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>66000</v>
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,10 +2160,10 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>6960</v>
+        <v>34800</v>
       </c>
       <c r="J43" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>34800</v>
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,10 +2277,10 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5250</v>
+        <v>21000</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>21000</v>
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-10</t>
+          <t>Steam 인기 차트 — 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3474,28 +3474,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cyberpunk 2077</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" t="n">
         <v>22265</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" t="n">
         <v>844921</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>19800</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>70</v>
+      <c r="F41" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3574,28 +3574,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>The Witcher 3: Wild Hunt</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" t="n">
         <v>15893</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" t="n">
         <v>835349</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>6960</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>80</v>
+      <c r="F45" t="n">
+        <v>34800</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="2" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="2" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="2" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>5250</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>75</v>
+      <c r="F48" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-10</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-10</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -834,10 +834,10 @@
         <v>1111720</v>
       </c>
       <c r="I9" t="n">
-        <v>64800</v>
+        <v>45360</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
         <v>64800</v>
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1107,10 +1107,10 @@
         <v>775883</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44800</v>
+        <v>33600</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>44800</v>
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-11</t>
+          <t>Steam 인기 차트 — 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -2724,28 +2724,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>15004</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>96.7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>1150098</v>
       </c>
-      <c r="F11" t="n">
-        <v>64800</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
+      <c r="F11" s="4" t="n">
+        <v>45360</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -2899,28 +2899,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>HELLDIVERS 2</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="4" t="n">
         <v>53399</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="4" t="n">
         <v>76.2</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>1017635</v>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>44800</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
+      <c r="F18" s="4" t="n">
+        <v>33600</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-11</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-11</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="J27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-12</t>
+          <t>Steam 인기 차트 — 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>50</v>
+      <c r="F29" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-12</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-12</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-13</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-13</t>
+          <t>Steam 인기 차트 — 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-13</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-13</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-14</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-14</t>
+          <t>Steam 인기 차트 — 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-14</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-14</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-15</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-15</t>
+          <t>Steam 인기 차트 — 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-15</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-15</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-16</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-16</t>
+          <t>Steam 인기 차트 — 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-16</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-16</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1107,10 +1107,10 @@
         <v>775883</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33600</v>
+        <v>44800</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>44800</v>
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-17</t>
+          <t>Steam 인기 차트 — 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2899,28 +2899,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>HELLDIVERS 2</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="2" t="n">
         <v>53399</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="2" t="n">
         <v>76.2</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="2" t="n">
         <v>1017635</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>33600</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>25</v>
+      <c r="F18" s="2" t="n">
+        <v>44800</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-17</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-17</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-18</t>
+          <t>Steam 인기 차트 — 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-18</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-18</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-19</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>24800</v>
+        <v>6200</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-19</t>
+          <t>Steam 인기 차트 — 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -3674,28 +3674,28 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="4" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" t="n">
-        <v>24800</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
+      <c r="F49" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-19</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-19</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-20</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-20</t>
+          <t>Steam 인기 차트 — 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-20</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-20</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-21</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-21</t>
+          <t>Steam 인기 차트 — 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-21</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-21</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-22</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-22</t>
+          <t>Steam 인기 차트 — 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-22</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-22</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-23</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-23</t>
+          <t>Steam 인기 차트 — 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-23</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-23</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>16500</v>
+        <v>10890</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-24</t>
+          <t>Steam 인기 차트 — 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="4" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
+      <c r="F31" s="4" t="n">
+        <v>10890</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-24</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-24</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-25</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>32000</v>
+        <v>22400</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -834,10 +834,10 @@
         <v>1111720</v>
       </c>
       <c r="I9" t="n">
-        <v>45360</v>
+        <v>64800</v>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>64800</v>
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2043,10 +2043,10 @@
         <v>630223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21500</v>
+        <v>8600</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21500</v>
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2160,19 +2160,19 @@
         <v>802993</v>
       </c>
       <c r="I43" t="n">
-        <v>34800</v>
+        <v>54900</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>34800</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2316,10 +2316,10 @@
         <v>844480</v>
       </c>
       <c r="I47" t="n">
-        <v>6200</v>
+        <v>24800</v>
       </c>
       <c r="J47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>24800</v>
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-25</t>
+          <t>Steam 인기 차트 — 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="F7" s="4" t="n">
+        <v>22400</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -2724,28 +2724,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Black Myth: Wukong</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" t="n">
         <v>15004</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" t="n">
         <v>96.7</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" t="n">
         <v>1150098</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>45360</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>30</v>
+      <c r="F11" t="n">
+        <v>64800</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3499,28 +3499,28 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="4" t="n">
         <v>44886</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="4" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>797216</v>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
+      <c r="F42" s="4" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3592,7 +3592,7 @@
         <v>835349</v>
       </c>
       <c r="F45" t="n">
-        <v>34800</v>
+        <v>54900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3674,28 +3674,28 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Euro Truck Simulator 2</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" t="n">
         <v>17281</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" t="n">
         <v>867404</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>75</v>
+      <c r="F49" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-25</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-25</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-26</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The Witcher 3: Wild Hunt</t>
+          <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-26</t>
+          <t>Steam 인기 차트 — 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Witcher 3: Wild Hunt</t>
+          <t>The Witcher 3: Wild Hunt - Complete Edition</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="4" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="4" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
+      <c r="F46" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-26</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-26</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-27</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>79800</v>
+        <v>7980</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-27</t>
+          <t>Steam 인기 차트 — 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="4" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" t="n">
-        <v>79800</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+      <c r="F43" s="4" t="n">
+        <v>7980</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="44">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-27</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-27</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-28</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-28</t>
+          <t>Steam 인기 차트 — 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-28</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-28</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-29</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>21500</v>
+        <v>15050</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-29</t>
+          <t>Steam 인기 차트 — 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="4" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
+      <c r="F51" s="4" t="n">
+        <v>15050</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-29</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-29</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-30</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1809,10 +1809,10 @@
         <v>594327</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10700</v>
+        <v>5350</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>10700</v>
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2043,10 +2043,10 @@
         <v>630223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8600</v>
+        <v>21500</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21500</v>
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-30</t>
+          <t>Steam 인기 차트 — 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3349,28 +3349,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PAYDAY 2</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="4" t="n">
         <v>27254</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="4" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>663082</v>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>10700</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
+      <c r="F36" s="4" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -3499,28 +3499,28 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Dead by Daylight</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="2" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="2" t="n">
         <v>797216</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>8600</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>60</v>
+      <c r="F42" s="2" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-30</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-30</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1224,10 +1224,10 @@
         <v>1373979</v>
       </c>
       <c r="I19" t="n">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
         <v>11000</v>
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>20500</v>
+        <v>4510</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-08-31</t>
+          <t>Steam 인기 차트 — 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -2974,28 +2974,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="4" t="n">
         <v>24580</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>1409473</v>
       </c>
-      <c r="F21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
+      <c r="F21" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -3274,28 +3274,28 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="4" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
+      <c r="F33" s="4" t="n">
+        <v>4510</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-08-31</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-08-31</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-01</t>
+          <t>Steam 인기 차트 — 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-01</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-01</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-02</t>
+          <t>Steam 인기 차트 — 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-02</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-02</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-03</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2082,10 +2082,10 @@
         <v>289966</v>
       </c>
       <c r="I41" t="n">
-        <v>7980</v>
+        <v>79800</v>
       </c>
       <c r="J41" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>79800</v>
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-03</t>
+          <t>Steam 인기 차트 — 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -3524,28 +3524,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hogwarts Legacy</t>
         </is>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" t="n">
         <v>5716</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" t="n">
         <v>90.2</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" t="n">
         <v>321395</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>7980</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>90</v>
+      <c r="F43" t="n">
+        <v>79800</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-03</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-03</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-04</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1419,10 +1419,10 @@
         <v>1122546</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10500</v>
+        <v>5250</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>10500</v>
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-04</t>
+          <t>Steam 인기 차트 — 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3099,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Garry's Mod</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="4" t="n">
         <v>18400</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="4" t="n">
         <v>96.8</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>1159707</v>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>10500</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
+      <c r="F26" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-04</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-04</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-05</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-05</t>
+          <t>Steam 인기 차트 — 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-05</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-05</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-06</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-06</t>
+          <t>Steam 인기 차트 — 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-06</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-06</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1068,10 +1068,10 @@
         <v>127273</v>
       </c>
       <c r="I15" t="n">
-        <v>45800</v>
+        <v>34350</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>45800</v>
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1224,10 +1224,10 @@
         <v>1373979</v>
       </c>
       <c r="I19" t="n">
-        <v>5500</v>
+        <v>11000</v>
       </c>
       <c r="J19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>11000</v>
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1614,10 +1614,10 @@
         <v>612177</v>
       </c>
       <c r="I29" t="n">
-        <v>10890</v>
+        <v>16500</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>16500</v>
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1692,10 +1692,10 @@
         <v>599805</v>
       </c>
       <c r="I31" t="n">
-        <v>4510</v>
+        <v>20500</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>20500</v>
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-07</t>
+          <t>Steam 인기 차트 — 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -2874,28 +2874,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Monster Hunter Wilds</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>12494</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>58.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>218415</v>
       </c>
-      <c r="F17" t="n">
-        <v>45800</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
+      <c r="F17" s="4" t="n">
+        <v>34350</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2974,28 +2974,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Terraria</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" t="n">
         <v>24580</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" t="n">
         <v>97.5</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" t="n">
         <v>1409473</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>50</v>
+      <c r="F21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3224,28 +3224,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ARK: Survival Evolved</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" t="n">
         <v>22170</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" t="n">
         <v>83.8</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" t="n">
         <v>730170</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>34</v>
+      <c r="F31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3274,28 +3274,28 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>The Forest</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" t="n">
         <v>2892</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" t="n">
         <v>95.5</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" t="n">
         <v>627791</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>4510</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>78</v>
+      <c r="F33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-07</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-07</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-08</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -678,10 +678,10 @@
         <v>358266</v>
       </c>
       <c r="I5" t="n">
-        <v>22400</v>
+        <v>32000</v>
       </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>32000</v>
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2199,10 +2199,10 @@
         <v>643681</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>5500</v>
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-08</t>
+          <t>Steam 인기 차트 — 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -2624,28 +2624,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Palworld</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" t="n">
         <v>18028</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" t="n">
         <v>380709</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>22400</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>30</v>
+      <c r="F7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3599,28 +3599,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Among Us</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>3832</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="2" t="n">
         <v>700785</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>40</v>
+      <c r="F46" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-08</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-08</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-09</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-09</t>
+          <t>Steam 인기 차트 — 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-09</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-09</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-10</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2277,10 +2277,10 @@
         <v>272900</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21000</v>
+        <v>5250</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>21000</v>
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-10</t>
+          <t>Steam 인기 차트 — 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -3649,28 +3649,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Borderlands 2</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="4" t="n">
         <v>8551</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="4" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>295218</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
+      <c r="F48" s="4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-10</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-10</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-11</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-11</t>
+          <t>Steam 인기 차트 — 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-11</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-11</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-12</t>
         </is>
       </c>
     </row>

--- a/steam_chart_tracker.xlsx
+++ b/steam_chart_tracker.xlsx
@@ -534,7 +534,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -573,7 +573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -651,7 +651,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -690,7 +690,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -768,7 +768,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -846,7 +846,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -885,7 +885,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -924,7 +924,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -963,7 +963,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1002,7 +1002,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1041,7 +1041,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1080,7 +1080,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1119,7 +1119,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1158,7 +1158,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1197,7 +1197,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1275,7 +1275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1314,7 +1314,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1353,7 +1353,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1392,7 +1392,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1431,7 +1431,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1470,7 +1470,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1509,7 +1509,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1536,10 +1536,10 @@
         <v>1071135</v>
       </c>
       <c r="I27" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
         <v>42000</v>
@@ -1548,7 +1548,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1587,7 +1587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1626,7 +1626,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1665,7 +1665,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1704,7 +1704,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1743,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1821,7 +1821,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1938,7 +1938,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1977,7 +1977,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2016,7 +2016,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2055,7 +2055,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2094,7 +2094,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2133,7 +2133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2172,7 +2172,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2211,7 +2211,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2250,7 +2250,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2289,7 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2328,7 +2328,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2367,7 +2367,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2394,10 +2394,10 @@
         <v>736611</v>
       </c>
       <c r="I49" t="n">
-        <v>15050</v>
+        <v>21500</v>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>21500</v>
@@ -2406,7 +2406,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2445,7 +2445,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2507,7 +2507,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Steam 인기 차트 — 2026-09-12</t>
+          <t>Steam 인기 차트 — 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3174,28 +3174,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="4" t="n">
         <v>143870</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>87.2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>1227784</v>
       </c>
-      <c r="F29" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
+      <c r="F29" s="4" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -3724,28 +3724,28 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Phasmophobia</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" t="n">
         <v>9978</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" t="n">
         <v>95.8</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" t="n">
         <v>768779</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>15050</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>30</v>
+      <c r="F51" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3830,7 +3830,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-12</t>
+          <t>2주(14일)+ 상위 50위 유지 게임 — 기준일: 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-12</t>
+          <t>4주(28일)+ 상위 50위 유지 게임 — 기준일: 2026-09-13</t>
         </is>
       </c>
     </row>
